--- a/Einzelabend_28.09.2026.xlsx
+++ b/Einzelabend_28.09.2026.xlsx
@@ -480,13 +480,13 @@
         <v>Küng</v>
       </c>
       <c r="D6">
-        <v>0.25</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="E6">
         <v>300</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>2</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8">
         <v>3</v>
@@ -639,7 +639,7 @@
         <v>Goonse</v>
       </c>
       <c r="D9">
-        <v>0.14285714285714285</v>
+        <v>0.125</v>
       </c>
       <c r="E9">
         <v>460</v>

--- a/Einzelabend_28.09.2026.xlsx
+++ b/Einzelabend_28.09.2026.xlsx
@@ -888,6 +888,20 @@
         <v>1</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Aufstehen</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" t="str">
         <v>Pünkt</v>
